--- a/AI Planning/Job Scheduling/Job To Machine/problemset/solution/ljf/delivery-10j-3m-1_10tr-lognormald-8c_ljf.xlsx
+++ b/AI Planning/Job Scheduling/Job To Machine/problemset/solution/ljf/delivery-10j-3m-1_10tr-lognormald-8c_ljf.xlsx
@@ -458,12 +458,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Calle 71J # 5-6 418990 Rivera, Huila</t>
+          <t>Carrera 28 # 11-73 Sur 201532 Gamarra, Cesar</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Oswaldo</t>
+          <t>William</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -479,61 +479,61 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Avenida calle 6ª # 1F-5 Sur Apto. 47 151834 Rondón, Boyacá</t>
+          <t>Avenida calle 33 # 86-5 Sur 172807 Filadelfia, Caldas</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Oswaldo</t>
+          <t>William</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Av. calle 1ª # 9-17 Este Oficina 7 504783 Acacías, Meta</t>
+          <t>Carrera 58 # 2-5 Sur Local 76 150278 Sutatenza, Boyacá</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Oswaldo</t>
+          <t>William</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
         <v>4</v>
-      </c>
-      <c r="E4" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Av. carrera 138 # 4-27 Este Casa 4 057725 Támesis, Antioquia</t>
+          <t>Calle 93O # 6-23 523742 La Tola, Nariño</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Oswaldo</t>
+          <t>William</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
         <v>7</v>
@@ -542,12 +542,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cl. 3ª # 13-2 Sur Torre 9 apartamento 8 208124 Gamarra, Cesar</t>
+          <t>Transversal 1 Este # 81-98 Este Apartamento 3 271247 El Cantón del San Pablo, Chocó</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eduardo</t>
+          <t>Alejandro</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -563,85 +563,85 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tr. 84 # 8-13 234462 Moñitos, Córdoba</t>
+          <t>Calle 84 # 6-90 Sur Casa 3 737876 Ambalema, Tolima</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Eduardo</t>
+          <t>Alejandro</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Calle 67 # 47-42 207191 Bosconia, Cesar</t>
+          <t>Carrera 132 Bis U # 3-56 Sur Apartamento 88 683527 San Joaquín, Santander</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Eduardo</t>
+          <t>Alejandro</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
         <v>7</v>
-      </c>
-      <c r="E8" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Av. Libia Leonor Guerrero # 1-3 Sur Local 58 445659 Albania, La Guajira</t>
+          <t>Cr. 54 # 21-76 Apto. 65 500190 Fuente de Oro, Meta</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Avenida Velásquez # 4-2 133646 San Jacinto del Cauca, Bolívar</t>
+          <t>Tr. 195N # 1-39 Este 543396 Villa Caro, Norte de Santander</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
